--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léonie joue au jardin, près de maman. La terre est fraîche. Léonie a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Léonie verse l'eau. Ça fait ploc. Maman dit : c'est l'heure. On va reprendre ses affaires avant de partir. Léonie cherche le seau. Elle le prend. Léonie cherche le manteau. Elle le prend. Léonie cherche le doudou. Elle le prend. Ses affaires sont dans ses mains. Maman dit : merci Léonie. Elles marchent vers la maison.</t>
+          <t>Léonie joue au jardin, près de maman. La terre est fraîche. Léonie a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Léonie verse l'eau. Ça fait ploc. C'est l'heure. On va reprendre ses affaires avant de partir. Léonie cherche le seau. Elle le prend. Léonie cherche le manteau. Elle le prend. Léonie cherche le doudou. Elle le prend. Ses affaires sont dans ses mains. Merci Léonie. Elles marchent vers la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léonie joue au jardin, près de maman. La terre est fraîche. Léonie a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Léonie verse l'eau. Ça fait ploc.
+maman|C'est l'heure. On va reprendre ses affaires avant de partir.
+narrateur|Léonie cherche le seau. Elle le prend. Léonie cherche le manteau. Elle le prend. Léonie cherche le doudou. Elle le prend. Ses affaires sont dans ses mains.
+maman|Merci Léonie.
+narrateur|Elles marchent vers la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Avant de partir, que fait Léonie ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léonie a cherché. Elle a repris le seau. Elle a repris le manteau. Elle a repris le doudou. C'était avant de partir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léonie tient le seau. Le doudou est contre elle. Maman est à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Elles marchent vers la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Avant de partir, que fait Léonie ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Léonie a cherché. Elle a repris le seau. Elle a repris le manteau. Elle a repris le doudou. C'était avant de partir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Léonie tient le seau. Le doudou est contre elle. Maman est à côté.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léonie reprend ses affaires au jardin</t>
+          <t>La gouttière et le seau vert</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AUT.RAN.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Au jardin, Sarah verse l'eau. Avant de partir, elle reprend seau, manteau et doudou.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léonie joue au jardin, près de maman. La terre est fraîche. Léonie a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Léonie verse l'eau. Ça fait ploc. C'est l'heure. On va reprendre ses affaires avant de partir. Léonie cherche le seau. Elle le prend. Léonie cherche le manteau. Elle le prend. Léonie cherche le doudou. Elle le prend. Ses affaires sont dans ses mains. Merci Léonie. Elles marchent vers la maison.</t>
+          <t>La gouttière fait plic, plic, plic. Une goutte tombe. Elle tombe dans la cuvette. La cuvette est grise. Tu entends, Sarah ? Plic, plic. Oui. Plic, plic. Maman essuie le rebord. Le bois est froid. Les bottes de Sarah attendent. Elles sont rouges. On met les bottes ? Oui, maman. Sarah enfile les bottes. En ce moment, Sarah est au jardin. La terre est fraîche. Les feuilles brillent. Maman est près du bac. Sarah a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Sarah verse l'eau. Ça fait ploc. Ploc, maman. Ploc, oui. Je t'écoute. L'eau coule un peu. La terre devient sombre. C'est l'heure. On reprend tes affaires avant de partir. Le seau ? Oui. Tu cherches le seau. Sarah cherche le seau. Elle le prend. J'ai le seau. Bravo, Sarah. Tu cherches le manteau. Sarah cherche le manteau. Elle le prend. Le manteau. Oui. Tu cherches le doudou. Sarah cherche le doudou. Elle le prend. Le doudou. Merci, Sarah. Tu as repris tes affaires. C'était avant de partir. Ses affaires sont dans ses mains. Elles marchent vers la maison. Les bottes font poum, poum. Tu tiens tout ? Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léonie joue au jardin, près de maman. La terre est fraîche. Léonie a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Léonie verse l'eau. Ça fait ploc.
-maman|C'est l'heure. On va reprendre ses affaires avant de partir.
-narrateur|Léonie cherche le seau. Elle le prend. Léonie cherche le manteau. Elle le prend. Léonie cherche le doudou. Elle le prend. Ses affaires sont dans ses mains.
-maman|Merci Léonie.
-narrateur|Elles marchent vers la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La gouttière fait plic, plic, plic.
+narrateur|Une goutte tombe.
+narrateur|Elle tombe dans la cuvette.
+narrateur|La cuvette est grise.
+maman|Tu entends, Sarah ?
+enfant-f|Plic, plic.
+maman|Oui.
+maman|Plic, plic.
+narrateur|Maman essuie le rebord.
+narrateur|Le bois est froid.
+narrateur|Les bottes de Sarah attendent.
+narrateur|Elles sont rouges.
+maman|On met les bottes ?
+enfant-f|Oui, maman.
+narrateur|Sarah enfile les bottes.
+narrateur|En ce moment, Sarah est au jardin.
+narrateur|La terre est fraîche.
+narrateur|Les feuilles brillent.
+narrateur|Maman est près du bac.
+narrateur|Sarah a un seau vert.
+narrateur|Elle a un manteau rouge.
+narrateur|Elle a son doudou beige.
+narrateur|Sarah verse l'eau.
+narrateur|Ça fait ploc.
+enfant-f|Ploc, maman.
+maman|Ploc, oui.
+maman|Je t'écoute.
+narrateur|L'eau coule un peu.
+narrateur|La terre devient sombre.
+maman|C'est l'heure.
+maman|On reprend tes affaires avant de partir.
+enfant-f|Le seau ?
+maman|Oui.
+maman|Tu cherches le seau.
+narrateur|Sarah cherche le seau.
+narrateur|Elle le prend.
+enfant-f|J'ai le seau.
+maman|Bravo, Sarah.
+maman|Tu cherches le manteau.
+narrateur|Sarah cherche le manteau.
+narrateur|Elle le prend.
+enfant-f|Le manteau.
+maman|Oui.
+maman|Tu cherches le doudou.
+narrateur|Sarah cherche le doudou.
+narrateur|Elle le prend.
+enfant-f|Le doudou.
+maman|Merci, Sarah.
+maman|Tu as repris tes affaires.
+maman|C'était avant de partir.
+narrateur|Ses affaires sont dans ses mains.
+narrateur|Elles marchent vers la maison.
+narrateur|Les bottes font poum, poum.
+maman|Tu tiens tout ?
+enfant-f|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Avant de partir, que fait Léonie ?</t>
+          <t>Avant de partir, que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1570,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Avant de partir, que fait Léonie ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Avant de partir, que fait Sarah ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léonie a cherché. Elle a repris le seau. Elle a repris le manteau. Elle a repris le doudou. C'était avant de partir.</t>
+          <t>Sarah a cherché. Elle a repris le seau. Elle a repris le manteau. Elle a repris le doudou. C'était avant de partir. Tu as tout, Sarah ? Oui. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1741,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léonie a cherché. Elle a repris le seau. Elle a repris le manteau. Elle a repris le doudou. C'était avant de partir.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a cherché.
+narrateur|Elle a repris le seau.
+narrateur|Elle a repris le manteau.
+narrateur|Elle a repris le doudou.
+narrateur|C'était avant de partir.
+maman|Tu as tout, Sarah ?
+enfant-f|Oui.
+maman|Bravo.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Léonie tient le seau. Le doudou est contre elle. Maman est à côté.</t>
+          <t>Sarah tient le seau. Le doudou est contre elle. Maman ouvre la porte. La gouttière fait encore plic. Tu poses le seau ? Sarah pose le seau. Elle pose le manteau. Merci, Sarah. Tu as repris tes affaires avant de partir. Oui, maman. Les bottes s'arrêtent. La maison est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1912,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Léonie tient le seau. Le doudou est contre elle. Maman est à côté.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah tient le seau.
+narrateur|Le doudou est contre elle.
+narrateur|Maman ouvre la porte.
+narrateur|La gouttière fait encore plic.
+maman|Tu poses le seau ?
+narrateur|Sarah pose le seau.
+narrateur|Elle pose le manteau.
+maman|Merci, Sarah.
+maman|Tu as repris tes affaires avant de partir.
+enfant-f|Oui, maman.
+narrateur|Les bottes s'arrêtent.
+narrateur|La maison est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1950,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai repris mes affaires. Avant de partir. Bravo, Sarah. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,10 +2090,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|J'ai repris mes affaires.
+maman|Avant de partir.
+maman|Bravo, Sarah.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière fait plic, plic, plic. Une goutte tombe. Elle tombe dans la cuvette. La cuvette est grise. Tu entends, Sarah ? Plic, plic. Oui. Plic, plic. Maman essuie le rebord. Le bois est froid. Les bottes de Sarah attendent. Elles sont rouges. On met les bottes ? Oui, maman. Sarah enfile les bottes. En ce moment, Sarah est au jardin. La terre est fraîche. Les feuilles brillent. Maman est près du bac. Sarah a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Sarah verse l'eau. Ça fait ploc. Ploc, maman. Ploc, oui. Je t'écoute. L'eau coule un peu. La terre devient sombre. C'est l'heure. On reprend tes affaires avant de partir. Le seau ? Oui. Tu cherches le seau. Sarah cherche le seau. Elle le prend. J'ai le seau. Bravo, Sarah. Tu cherches le manteau. Sarah cherche le manteau. Elle le prend. Le manteau. Oui. Tu cherches le doudou. Sarah cherche le doudou. Elle le prend. Le doudou. Merci, Sarah. Tu as repris tes affaires. C'était avant de partir. Ses affaires sont dans ses mains. Elles marchent vers la maison. Les bottes font poum, poum. Tu tiens tout ? Oui.</t>
+          <t>La gouttière fait plic, plic, plic. Une goutte tombe. Elle tombe dans la cuvette. La cuvette est grise. Tu entends, Sarah ? Plic, plic. Oui. Plic, plic. Maman essuie le rebord. Le bois est froid. Les bottes de Sarah attendent. Elles sont rouges. On met les bottes ? Oui, maman. Sarah enfile les bottes. On va au jardin ? Oui. La porte s'ouvre. En ce moment, Sarah est au jardin. La terre est fraîche. Les feuilles brillent. Je m'assois près du bac. Sarah a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Sarah verse l'eau. Ça fait ploc. Ploc, maman. Ploc, oui. Je t'écoute. Sarah verse encore. Ça fait ploc, ploc. Le seau est mouillé. Tes mains sont froides ? Un peu. L'eau coule un peu. La terre devient sombre. C'est l'heure. On reprend tes affaires avant de partir. Le seau ? Oui. Tu cherches le seau. Sarah cherche le seau. Elle le prend. J'ai le seau. Bravo, Sarah. Tu cherches le manteau. Sarah cherche le manteau. Elle le prend. Le manteau. Oui. Tu cherches le doudou. Sarah cherche le doudou. Elle le prend. Le doudou. Merci, Sarah. Tu as repris tes affaires. C'était avant de partir. Ses affaires sont dans ses mains. Elles marchent vers la maison. Les bottes font poum, poum. Tu tiens tout ? Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1344,10 +1344,13 @@
 maman|On met les bottes ?
 enfant-f|Oui, maman.
 narrateur|Sarah enfile les bottes.
+maman|On va au jardin ?
+enfant-f|Oui.
+narrateur|La porte s'ouvre.
 narrateur|En ce moment, Sarah est au jardin.
 narrateur|La terre est fraîche.
 narrateur|Les feuilles brillent.
-narrateur|Maman est près du bac.
+maman|Je m'assois près du bac.
 narrateur|Sarah a un seau vert.
 narrateur|Elle a un manteau rouge.
 narrateur|Elle a son doudou beige.
@@ -1356,6 +1359,11 @@
 enfant-f|Ploc, maman.
 maman|Ploc, oui.
 maman|Je t'écoute.
+narrateur|Sarah verse encore.
+narrateur|Ça fait ploc, ploc.
+narrateur|Le seau est mouillé.
+maman|Tes mains sont froides ?
+enfant-f|Un peu.
 narrateur|L'eau coule un peu.
 narrateur|La terre devient sombre.
 maman|C'est l'heure.
@@ -1776,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah tient le seau. Le doudou est contre elle. Maman ouvre la porte. La gouttière fait encore plic. Tu poses le seau ? Sarah pose le seau. Elle pose le manteau. Merci, Sarah. Tu as repris tes affaires avant de partir. Oui, maman. Les bottes s'arrêtent. La maison est calme.</t>
+          <t>Sarah tient le seau. Le doudou est contre elle. Maman ouvre la porte. La gouttière fait encore plic. Tu poses le seau ? Sarah pose le seau. Elle pose le manteau. Merci, Sarah. Tu as repris tes affaires avant de partir. Oui, maman. Les bottes s'arrêtent. La maison est calme. Tu poses les bottes ? Sarah pose les bottes. Elles sont un peu mouillées. Bravo, Sarah.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1923,7 +1931,11 @@
 maman|Tu as repris tes affaires avant de partir.
 enfant-f|Oui, maman.
 narrateur|Les bottes s'arrêtent.
-narrateur|La maison est calme.</t>
+narrateur|La maison est calme.
+maman|Tu poses les bottes ?
+narrateur|Sarah pose les bottes.
+narrateur|Elles sont un peu mouillées.
+maman|Bravo, Sarah.</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2169,41 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La gouttière et le seau vert</t>
+          <t>Les gouttes du seau vert</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Au jardin, Sarah verse l'eau. Avant de partir, elle reprend seau, manteau et doudou.</t>
+          <t>Sarah veut remplir le seau vert avec les gouttes. Pour donner de l'eau au doudou à la maison, elle reprend seau, manteau et doudou.</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière fait plic, plic, plic. Une goutte tombe. Elle tombe dans la cuvette. La cuvette est grise. Tu entends, Sarah ? Plic, plic. Oui. Plic, plic. Maman essuie le rebord. Le bois est froid. Les bottes de Sarah attendent. Elles sont rouges. On met les bottes ? Oui, maman. Sarah enfile les bottes. On va au jardin ? Oui. La porte s'ouvre. En ce moment, Sarah est au jardin. La terre est fraîche. Les feuilles brillent. Je m'assois près du bac. Sarah a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Sarah verse l'eau. Ça fait ploc. Ploc, maman. Ploc, oui. Je t'écoute. Sarah verse encore. Ça fait ploc, ploc. Le seau est mouillé. Tes mains sont froides ? Un peu. L'eau coule un peu. La terre devient sombre. C'est l'heure. On reprend tes affaires avant de partir. Le seau ? Oui. Tu cherches le seau. Sarah cherche le seau. Elle le prend. J'ai le seau. Bravo, Sarah. Tu cherches le manteau. Sarah cherche le manteau. Elle le prend. Le manteau. Oui. Tu cherches le doudou. Sarah cherche le doudou. Elle le prend. Le doudou. Merci, Sarah. Tu as repris tes affaires. C'était avant de partir. Ses affaires sont dans ses mains. Elles marchent vers la maison. Les bottes font poum, poum. Tu tiens tout ? Oui.</t>
+          <t>La gouttière fait plic, plic, plic. Une goutte tombe. Elle tombe dans la cuvette. La cuvette est grise. Tu entends, Sarah ? Plic, plic. Oui. Plic, plic. Maman essuie le rebord. Le bois est froid. Les bottes de Sarah attendent. Elles sont rouges. On met les bottes ? Oui, maman. Sarah enfile les bottes. On va au jardin ? Oui. Pour l'eau. La porte s'ouvre. En ce moment, Sarah est au jardin. La terre est fraîche. Les feuilles brillent. Je m'assois près du bac. Sarah a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. De l'eau pour lui. Pour le doudou ? Oui. Sarah verse l'eau. Ça fait ploc. Ploc, maman. Ploc, oui. Je t'écoute. Sarah verse encore. Ça fait ploc, ploc. Le seau est mouillé. Tes mains sont froides ? Un peu. L'eau coule un peu. La terre devient sombre. Le doudou est sur la terre. C'est l'heure. On reprend ses affaires, avant de partir. Le seau ? Oui. Tu cherches le seau. Sarah cherche le seau. Elle le prend. J'ai le seau. Bien. L'eau vient à la maison. Le manteau est sur la chaise. Le doudou est sur la terre. Une oreille est un peu mouillée.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léonie joue au jardin, près de maman. La terre est fraîche. Léonie a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Léonie verse l'eau. Ça fait ploc. Maman dit : c'est l'heure. On va &lt;emphasis level="moderate"&gt;reprendre&lt;/emphasis&gt; ses affaires avant de partir. Léonie cherche le seau. Elle le prend. Léonie cherche le manteau. Elle le prend. Léonie cherche le doudou. Elle le prend. Ses affaires sont dans ses mains. Maman dit : merci Léonie. Elles marchent vers la maison.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gouttière fait plic, plic, plic. Une goutte tombe. Elle tombe dans la cuvette. La cuvette est grise. Tu entends, Sarah ? Plic, plic. Oui. Plic, plic. Maman essuie le rebord. Le bois est froid. Les bottes de Sarah attendent. Elles sont rouges. On met les bottes ? Oui, maman. Sarah enfile les bottes. On va au jardin ? Oui. Pour l'eau. La porte s'ouvre. En ce moment, Sarah est au jardin. La terre est fraîche. Les feuilles brillent. Je m'assois près du bac. Sarah a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. De l'eau pour lui. Pour le doudou ? Oui. Sarah verse l'eau. Ça fait ploc. Ploc, maman. Ploc, oui. Je t'écoute. Sarah verse encore. Ça fait ploc, ploc. Le seau est mouillé. Tes mains sont froides ? Un peu. L'eau coule un peu. La terre devient sombre. Le doudou est sur la terre. C'est l'heure. On reprend ses affaires, avant de partir. Le seau ? Oui. Tu cherches le seau. Sarah cherche le seau. Elle le prend. J'ai le seau. Bien. L'eau vient à la maison. Le manteau est sur la chaise. Le doudou est sur la terre. Une oreille est un peu mouillée.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1346,6 +1346,7 @@
 narrateur|Sarah enfile les bottes.
 maman|On va au jardin ?
 enfant-f|Oui.
+enfant-f|Pour l'eau.
 narrateur|La porte s'ouvre.
 narrateur|En ce moment, Sarah est au jardin.
 narrateur|La terre est fraîche.
@@ -1354,6 +1355,9 @@
 narrateur|Sarah a un seau vert.
 narrateur|Elle a un manteau rouge.
 narrateur|Elle a son doudou beige.
+enfant-f|De l'eau pour lui.
+maman|Pour le doudou ?
+enfant-f|Oui.
 narrateur|Sarah verse l'eau.
 narrateur|Ça fait ploc.
 enfant-f|Ploc, maman.
@@ -1366,32 +1370,20 @@
 enfant-f|Un peu.
 narrateur|L'eau coule un peu.
 narrateur|La terre devient sombre.
+narrateur|Le doudou est sur la terre.
 maman|C'est l'heure.
-maman|On reprend tes affaires avant de partir.
+maman|On reprend ses affaires, avant de partir.
 enfant-f|Le seau ?
 maman|Oui.
 maman|Tu cherches le seau.
 narrateur|Sarah cherche le seau.
 narrateur|Elle le prend.
 enfant-f|J'ai le seau.
-maman|Bravo, Sarah.
-maman|Tu cherches le manteau.
-narrateur|Sarah cherche le manteau.
-narrateur|Elle le prend.
-enfant-f|Le manteau.
-maman|Oui.
-maman|Tu cherches le doudou.
-narrateur|Sarah cherche le doudou.
-narrateur|Elle le prend.
-enfant-f|Le doudou.
-maman|Merci, Sarah.
-maman|Tu as repris tes affaires.
-maman|C'était avant de partir.
-narrateur|Ses affaires sont dans ses mains.
-narrateur|Elles marchent vers la maison.
-narrateur|Les bottes font poum, poum.
-maman|Tu tiens tout ?
-enfant-f|Oui.</t>
+maman|Bien.
+maman|L'eau vient à la maison.
+narrateur|Le manteau est sur la chaise.
+narrateur|Le doudou est sur la terre.
+narrateur|Une oreille est un peu mouillée.</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;&lt;emphasis level="moderate"&gt;avant&lt;/emphasis&gt; de partir, que fait Léonie ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Avant de partir, que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1438,7 +1430,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>reprendre | ses affaires | elle reprend | avant de partir</t>
+          <t>reprendre | ses affaires | il reprend | elle reprend | avant de partir</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1453,7 +1445,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle reprend ses affaires. Que fait Léonie ?</t>
+          <t>Elle reprend ses affaires. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1605,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a cherché. Elle a repris le seau. Elle a repris le manteau. Elle a repris le doudou. C'était avant de partir. Tu as tout, Sarah ? Oui. Bravo. C'est du bon travail.</t>
+          <t>Sarah cherche le manteau. Elle le prend. Le manteau. Oui. Tu cherches le doudou. Sarah cherche le doudou. Elle le prend. Le doudou. Son oreille est mouillée. Un peu. Tu as repris tes affaires. Avant de partir. Oui. Ses affaires sont dans ses mains. Elles marchent vers la maison. Les bottes font poum, poum. Tu tiens tout ? Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léonie a cherché. Elle a repris le seau. Elle a repris le manteau. Elle a repris le doudou. C'était &lt;emphasis level="moderate"&gt;avant&lt;/emphasis&gt; de partir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah cherche le manteau. Elle le prend. Le manteau. Oui. Tu cherches le doudou. Sarah cherche le doudou. Elle le prend. Le doudou. Son oreille est mouillée. Un peu. Tu as repris tes affaires. Avant de partir. Oui. Ses affaires sont dans ses mains. Elles marchent vers la maison. Les bottes font poum, poum. Tu tiens tout ? Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,15 +1741,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a cherché.
-narrateur|Elle a repris le seau.
-narrateur|Elle a repris le manteau.
-narrateur|Elle a repris le doudou.
-narrateur|C'était avant de partir.
-maman|Tu as tout, Sarah ?
-enfant-f|Oui.
-maman|Bravo.
-maman|C'est du bon travail.</t>
+          <t>narrateur|Sarah cherche le manteau.
+narrateur|Elle le prend.
+enfant-f|Le manteau.
+maman|Oui.
+maman|Tu cherches le doudou.
+narrateur|Sarah cherche le doudou.
+narrateur|Elle le prend.
+enfant-f|Le doudou.
+maman|Son oreille est mouillée.
+enfant-f|Un peu.
+maman|Tu as repris tes affaires.
+enfant-f|Avant de partir.
+maman|Oui.
+narrateur|Ses affaires sont dans ses mains.
+narrateur|Elles marchent vers la maison.
+narrateur|Les bottes font poum, poum.
+maman|Tu tiens tout ?
+enfant-f|Oui.</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1785,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah tient le seau. Le doudou est contre elle. Maman ouvre la porte. La gouttière fait encore plic. Tu poses le seau ? Sarah pose le seau. Elle pose le manteau. Merci, Sarah. Tu as repris tes affaires avant de partir. Oui, maman. Les bottes s'arrêtent. La maison est calme. Tu poses les bottes ? Sarah pose les bottes. Elles sont un peu mouillées. Bravo, Sarah.</t>
+          <t>Sarah tient le seau. Le doudou est contre elle. Maman ouvre la porte. La gouttière fait encore plic. Tu poses le seau ? Sarah pose le seau. Elle pose le manteau. Merci, Sarah. On donne de l'eau au doudou ? Oui, maman. Maman prend une soucoupe. Sarah verse une goutte. Ploc. Il boit. Bravo. Tu as repris tes affaires. Les bottes s'arrêtent. La maison est calme. Tu poses les bottes ? Sarah pose les bottes. Elles sont un peu mouillées.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léonie tient le seau. Le doudou est contre elle. Maman est à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah tient le seau. Le doudou est contre elle. Maman ouvre la porte. La gouttière fait encore plic. Tu poses le seau ? Sarah pose le seau. Elle pose le manteau. Merci, Sarah. On donne de l'eau au doudou ? Oui, maman. Maman prend une soucoupe. Sarah verse une goutte. Ploc. Il boit. Bravo. Tu as repris tes affaires. Les bottes s'arrêtent. La maison est calme. Tu poses les bottes ? Sarah pose les bottes. Elles sont un peu mouillées.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1928,14 +1929,19 @@
 narrateur|Sarah pose le seau.
 narrateur|Elle pose le manteau.
 maman|Merci, Sarah.
-maman|Tu as repris tes affaires avant de partir.
+maman|On donne de l'eau au doudou ?
 enfant-f|Oui, maman.
+narrateur|Maman prend une soucoupe.
+narrateur|Sarah verse une goutte.
+narrateur|Ploc.
+enfant-f|Il boit.
+maman|Bravo.
+maman|Tu as repris tes affaires.
 narrateur|Les bottes s'arrêtent.
 narrateur|La maison est calme.
 maman|Tu poses les bottes ?
 narrateur|Sarah pose les bottes.
-narrateur|Elles sont un peu mouillées.
-maman|Bravo, Sarah.</t>
+narrateur|Elles sont un peu mouillées.</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1968,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai repris mes affaires. Avant de partir. Bravo, Sarah. L'histoire est finie.</t>
+          <t>Le doudou a de l'eau. Et toi, tu as repris tes affaires. La gouttière fait encore plic. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le doudou a de l'eau. Et toi, tu as repris tes affaires. La gouttière fait encore plic. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,9 +2108,9 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai repris mes affaires.
-maman|Avant de partir.
-maman|Bravo, Sarah.
+          <t>enfant-f|Le doudou a de l'eau.
+maman|Et toi, tu as repris tes affaires.
+narrateur|La gouttière fait encore plic.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2126,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2206,6 +2212,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a de l'eau. Et toi, tu as repris tes affaires. La gouttière fait encore plic. L'histoire est finie.</t>
+          <t>Le doudou a de l'eau. Et toi, tu as repris tes affaires. La gouttière fait encore plic.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a de l'eau. Et toi, tu as repris tes affaires. La gouttière fait encore plic. L'histoire est finie.</t>
+          <t>Le doudou a de l'eau. Et toi, tu as repris tes affaires. La gouttière fait encore plic.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2110,8 +2110,7 @@
         <is>
           <t>enfant-f|Le doudou a de l'eau.
 maman|Et toi, tu as repris tes affaires.
-narrateur|La gouttière fait encore plic.
-narrateur|L'histoire est finie.</t>
+narrateur|La gouttière fait encore plic.</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2217,6 +2216,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>rebord de fenêtre puis jardin après la pluie</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léonie, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah veut remplir le seau vert avec les gouttes. Pour donner de l'eau au doudou à la maison, elle reprend seau, manteau et doudou.</t>
+          <t>Le zinc tic. Un point de gouttière brille sous une goutte. Sarah veut l'eau maintenant, dans le seau vert, pour le doudou. Elle pousse trop vite : l'eau gicle, le seau reste vide. Elle refuse de forcer, reprend seau, manteau, doudou. Au jardin, le seau penche. Elle refuse de foncer, retrouve le point. L'eau paie le début.</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière fait plic, plic, plic. Une goutte tombe. Elle tombe dans la cuvette. La cuvette est grise. Tu entends, Sarah ? Plic, plic. Oui. Plic, plic. Maman essuie le rebord. Le bois est froid. Les bottes de Sarah attendent. Elles sont rouges. On met les bottes ? Oui, maman. Sarah enfile les bottes. On va au jardin ? Oui. Pour l'eau. La porte s'ouvre. En ce moment, Sarah est au jardin. La terre est fraîche. Les feuilles brillent. Je m'assois près du bac. Sarah a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. De l'eau pour lui. Pour le doudou ? Oui. Sarah verse l'eau. Ça fait ploc. Ploc, maman. Ploc, oui. Je t'écoute. Sarah verse encore. Ça fait ploc, ploc. Le seau est mouillé. Tes mains sont froides ? Un peu. L'eau coule un peu. La terre devient sombre. Le doudou est sur la terre. C'est l'heure. On reprend ses affaires, avant de partir. Le seau ? Oui. Tu cherches le seau. Sarah cherche le seau. Elle le prend. J'ai le seau. Bien. L'eau vient à la maison. Le manteau est sur la chaise. Le doudou est sur la terre. Une oreille est un peu mouillée.</t>
+          <t>Le zinc de la gouttière fait tic. Une goutte y tient, ronde. Sous la goutte, un point de gouttière brille. Sarah connaît ce rebord, après la pluie. Le bois du rebord est froid. Ça sent le bois mouillé. Derrière la vitre, le jardin luisant attend. Maman essuie le rebord, sans presser. Un carré de ciel pâle touche le zinc. Maman, le point brille ! Oui. Il est sur le zinc. La cuvette grise attend dessous. Plic. La goutte tombe dans la cuvette. Un seau vert dort près des bottes. Les bottes de Sarah sont rouges. Le doudou beige est sur la chaise. Un manteau rouge pend au crochet. Je veux l'eau, maintenant ! Pour lui, dans le seau ! Tu la veux vite ? Oui, maman. En ce moment, Sarah saisit le seau vert. Le plastique est froid, un peu rêche. Elle court vers le rebord. Le seau tape contre sa jambe. Je le mets sous le zinc ! Elle pousse le seau, trop vite. L'eau gicle sur le bois. Oh. Le seau reste presque vide. Une manche du manteau tombe. Le manteau rouge glisse du crochet. Le doudou beige roule vers le pot. Ça ne veut pas. Le sourire de Sarah disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Maman se baisse à sa hauteur. Tu regardes le seau ? Sarah ramasse le seau, sans crier. Je le reprends.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La gouttière fait plic, plic, plic. Une goutte tombe. Elle tombe dans la cuvette. La cuvette est grise. Tu entends, Sarah ? Plic, plic. Oui. Plic, plic. Maman essuie le rebord. Le bois est froid. Les bottes de Sarah attendent. Elles sont rouges. On met les bottes ? Oui, maman. Sarah enfile les bottes. On va au jardin ? Oui. Pour l'eau. La porte s'ouvre. En ce moment, Sarah est au jardin. La terre est fraîche. Les feuilles brillent. Je m'assois près du bac. Sarah a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. De l'eau pour lui. Pour le doudou ? Oui. Sarah verse l'eau. Ça fait ploc. Ploc, maman. Ploc, oui. Je t'écoute. Sarah verse encore. Ça fait ploc, ploc. Le seau est mouillé. Tes mains sont froides ? Un peu. L'eau coule un peu. La terre devient sombre. Le doudou est sur la terre. C'est l'heure. On reprend ses affaires, avant de partir. Le seau ? Oui. Tu cherches le seau. Sarah cherche le seau. Elle le prend. J'ai le seau. Bien. L'eau vient à la maison. Le manteau est sur la chaise. Le doudou est sur la terre. Une oreille est un peu mouillée.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le zinc de la gouttière fait tic. Une goutte y tient, ronde. Sous la goutte, un &lt;emphasis level="moderate"&gt;point de gouttière&lt;/emphasis&gt; brille. Sarah connaît ce rebord, après la pluie. Le bois du rebord est froid. Ça sent le bois mouillé. Derrière la vitre, le jardin luisant attend. Maman essuie le rebord, sans presser. Un carré de ciel pâle touche le zinc. Maman, le point brille ! Oui. Il est sur le zinc. La cuvette grise attend dessous. Plic. La goutte tombe dans la cuvette. Un seau vert dort près des bottes. Les bottes de Sarah sont rouges. Le doudou beige est sur la chaise. Un manteau rouge pend au crochet. Je veux l'eau, maintenant ! Pour lui, dans le seau ! Tu la veux vite ? Oui, maman. En ce moment, Sarah saisit le seau vert. Le plastique est froid, un peu rêche. Elle court vers le rebord. Le seau tape contre sa jambe. Je le mets sous le zinc ! Elle pousse le seau, trop vite. L'eau gicle sur le bois. Oh. Le seau reste presque vide. Une manche du manteau tombe. Le manteau rouge glisse du crochet. Le doudou beige roule vers le pot. Ça ne veut pas. Le sourire de Sarah disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Maman se baisse à sa hauteur. Tu regardes le seau ? Sarah ramasse le seau, sans crier. Je le reprends.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Léonie joue au jardin, près de maman. La terre est fraîche. Léonie a un seau vert. Elle a un manteau rouge. Elle a son doudou beige. Léonie verse l'eau. Ça fait ploc. Maman dit : c'est l'heure. On va &lt;emphasis&gt;reprendre&lt;/emphasis&gt; ses affaires avant de partir. Léonie cherche le seau. Elle le prend. Léonie cherche le manteau. Elle le prend. Léonie cherche le doudou. Elle le prend. Ses affaires sont dans ses mains. Maman dit : merci Léonie. Elles marchent vers la maison.&lt;/slow&gt; [pause]</t>
+          <t>Le zinc de la gouttière fait tic. Une goutte y tient, ronde. Sous la goutte, un &lt;emphasis&gt;point de gouttière&lt;/emphasis&gt; brille. Sarah connaît ce rebord, après la pluie. Le bois du rebord est froid. Ça sent le bois mouillé. Derrière la vitre, le jardin luisant attend. Maman essuie le rebord, sans presser. Un carré de ciel pâle touche le zinc. Maman, le point brille ! Oui. Il est sur le zinc. La cuvette grise attend dessous. Plic. La goutte tombe dans la cuvette. Un seau vert dort près des bottes. Les bottes de Sarah sont rouges. Le doudou beige est sur la chaise. Un manteau rouge pend au crochet. Je veux l'eau, maintenant ! Pour lui, dans le seau ! Tu la veux vite ? Oui, maman. En ce moment, Sarah saisit le seau vert. Le plastique est froid, un peu rêche. Elle court vers le rebord. Le seau tape contre sa jambe. Je le mets sous le zinc ! Elle pousse le seau, trop vite. L'eau gicle sur le bois. Oh. Le seau reste presque vide. Une manche du manteau tombe. Le manteau rouge glisse du crochet. Le doudou beige roule vers le pot. Ça ne veut pas. Le sourire de Sarah disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Maman se baisse à sa hauteur. Tu regardes le seau ? Sarah ramasse le seau, sans crier. Je le reprends. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1246,18 +1246,18 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1280,30 +1280,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>reprendre</t>
+          <t>point de gouttière</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1324,66 +1324,62 @@
         <v>50</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_l_eau_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La gouttière fait plic, plic, plic.
-narrateur|Une goutte tombe.
-narrateur|Elle tombe dans la cuvette.
-narrateur|La cuvette est grise.
-maman|Tu entends, Sarah ?
-enfant-f|Plic, plic.
+          <t>narrateur|Le zinc de la gouttière fait tic.
+narrateur|Une goutte y tient, ronde.
+narrateur|Sous la goutte, un point de gouttière brille.
+narrateur|Sarah connaît ce rebord, après la pluie.
+narrateur|Le bois du rebord est froid.
+narrateur|Ça sent le bois mouillé.
+narrateur|Derrière la vitre, le jardin luisant attend.
+narrateur|Maman essuie le rebord, sans presser.
+narrateur|Un carré de ciel pâle touche le zinc.
+enfant-f|Maman, le point brille !
 maman|Oui.
-maman|Plic, plic.
-narrateur|Maman essuie le rebord.
-narrateur|Le bois est froid.
-narrateur|Les bottes de Sarah attendent.
-narrateur|Elles sont rouges.
-maman|On met les bottes ?
+maman|Il est sur le zinc.
+narrateur|La cuvette grise attend dessous.
+narrateur|Plic.
+narrateur|La goutte tombe dans la cuvette.
+narrateur|Un seau vert dort près des bottes.
+narrateur|Les bottes de Sarah sont rouges.
+narrateur|Le doudou beige est sur la chaise.
+narrateur|Un manteau rouge pend au crochet.
+enfant-f|Je veux l'eau, maintenant !
+enfant-f|Pour lui, dans le seau !
+maman|Tu la veux vite ?
 enfant-f|Oui, maman.
-narrateur|Sarah enfile les bottes.
-maman|On va au jardin ?
-enfant-f|Oui.
-enfant-f|Pour l'eau.
-narrateur|La porte s'ouvre.
-narrateur|En ce moment, Sarah est au jardin.
-narrateur|La terre est fraîche.
-narrateur|Les feuilles brillent.
-maman|Je m'assois près du bac.
-narrateur|Sarah a un seau vert.
-narrateur|Elle a un manteau rouge.
-narrateur|Elle a son doudou beige.
-enfant-f|De l'eau pour lui.
-maman|Pour le doudou ?
-enfant-f|Oui.
-narrateur|Sarah verse l'eau.
-narrateur|Ça fait ploc.
-enfant-f|Ploc, maman.
-maman|Ploc, oui.
-maman|Je t'écoute.
-narrateur|Sarah verse encore.
-narrateur|Ça fait ploc, ploc.
-narrateur|Le seau est mouillé.
-maman|Tes mains sont froides ?
-enfant-f|Un peu.
-narrateur|L'eau coule un peu.
-narrateur|La terre devient sombre.
-narrateur|Le doudou est sur la terre.
-maman|C'est l'heure.
-maman|On reprend ses affaires, avant de partir.
-enfant-f|Le seau ?
-maman|Oui.
-maman|Tu cherches le seau.
-narrateur|Sarah cherche le seau.
-narrateur|Elle le prend.
-enfant-f|J'ai le seau.
-maman|Bien.
-maman|L'eau vient à la maison.
-narrateur|Le manteau est sur la chaise.
-narrateur|Le doudou est sur la terre.
-narrateur|Une oreille est un peu mouillée.</t>
+narrateur|En ce moment, Sarah saisit le seau vert.
+narrateur|Le plastique est froid, un peu rêche.
+narrateur|Elle court vers le rebord.
+narrateur|Le seau tape contre sa jambe.
+enfant-f|Je le mets sous le zinc !
+narrateur|Elle pousse le seau, trop vite.
+narrateur|L'eau gicle sur le bois.
+enfant-f|Oh.
+narrateur|Le seau reste presque vide.
+narrateur|Une manche du manteau tombe.
+narrateur|Le manteau rouge glisse du crochet.
+narrateur|Le doudou beige roule vers le pot.
+enfant-f|Ça ne veut pas.
+narrateur|Le sourire de Sarah disparaît.
+narrateur|Dans sa poitrine, envie et inquiétude se bousculent.
+narrateur|Maman se baisse à sa hauteur.
+maman|Tu regardes le seau ?
+narrateur|Sarah ramasse le seau, sans crier.
+enfant-f|Je le reprends.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>gouttiere,goutte,seau</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1411,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Avant de partir, que fait Sarah ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Avant de &lt;emphasis level="moderate"&gt;partir&lt;/emphasis&gt;, que fait Sarah ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;&lt;emphasis&gt;avant&lt;/emphasis&gt; de partir, que fait Léonie ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Avant de &lt;emphasis&gt;partir&lt;/emphasis&gt;, que fait Sarah ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1483,7 +1479,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1491,10 +1487,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1509,38 +1505,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
-          <t>avant</t>
+          <t>partir</t>
         </is>
       </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1549,13 +1545,13 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
@@ -1565,7 +1561,7 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=elle_reprend_avant_de_partir; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1597,17 +1593,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah cherche le manteau. Elle le prend. Le manteau. Oui. Tu cherches le doudou. Sarah cherche le doudou. Elle le prend. Le doudou. Son oreille est mouillée. Un peu. Tu as repris tes affaires. Avant de partir. Oui. Ses affaires sont dans ses mains. Elles marchent vers la maison. Les bottes font poum, poum. Tu tiens tout ? Oui.</t>
+          <t>Sarah refuse de pousser plus fort. Elle pose un genou au sol. Le seau vert est froid, vide. Je le tiens. Le manteau, près du crochet ? Sarah se penche. Le manteau rouge est un peu mouillé. Elle le prend, sans tirer. Le manteau. Oui. Le doudou beige attend près du pot. Toi aussi. Elle le ramasse, une oreille mouillée. Son oreille est froide. Tu le serres ? Oui, maman. Sarah appuie le seau contre sa hanche. Le plastique fait un petit clic. On met tes bottes ? Sarah enfile ses bottes rouges. Une semelle est froide. Tu as fini tes bottes ? Oui, maman. Tu tiens tout ? Oui. Merci, Sarah. Le seau est prêt ? Oui, maman. Sarah pose la main sur le bord. Le bord est un peu rêche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah cherche le manteau. Elle le prend. Le manteau. Oui. Tu cherches le doudou. Sarah cherche le doudou. Elle le prend. Le doudou. Son oreille est mouillée. Un peu. Tu as repris tes affaires. Avant de partir. Oui. Ses affaires sont dans ses mains. Elles marchent vers la maison. Les bottes font poum, poum. Tu tiens tout ? Oui.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah refuse de pousser plus fort. Elle pose un genou au sol. Le &lt;emphasis level="moderate"&gt;seau&lt;/emphasis&gt; vert est froid, vide. Je le tiens. Le manteau, près du crochet ? Sarah se penche. Le manteau rouge est un peu mouillé. Elle le prend, sans tirer. Le manteau. Oui. Le doudou beige attend près du pot. Toi aussi. Elle le ramasse, une oreille mouillée. Son oreille est froide. Tu le serres ? Oui, maman. Sarah appuie le seau contre sa hanche. Le plastique fait un petit clic. On met tes bottes ? Sarah enfile ses bottes rouges. Une semelle est froide. Tu as fini tes bottes ? Oui, maman. Tu tiens tout ? Oui. Merci, Sarah. Le seau est prêt ? Oui, maman. Sarah pose la main sur le bord. Le bord est un peu rêche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Léonie a cherché. Elle a repris le seau. Elle a repris le manteau. Elle a repris le doudou. C'était &lt;emphasis&gt;avant&lt;/emphasis&gt; de partir.&lt;/slow&gt; [pause]</t>
+          <t>Sarah refuse de pousser plus fort. Elle pose un genou au sol. Le &lt;emphasis&gt;seau&lt;/emphasis&gt; vert est froid, vide. Je le tiens. Le manteau, près du crochet ? Sarah se penche. Le manteau rouge est un peu mouillé. Elle le prend, sans tirer. Le manteau. Oui. Le doudou beige attend près du pot. Toi aussi. Elle le ramasse, une oreille mouillée. Son oreille est froide. Tu le serres ? Oui, maman. Sarah appuie le seau contre sa hanche. Le plastique fait un petit clic. On met tes bottes ? Sarah enfile ses bottes rouges. Une semelle est froide. Tu as fini tes bottes ? Oui, maman. Tu tiens tout ? Oui. Merci, Sarah. Le seau est prêt ? Oui, maman. Sarah pose la main sur le bord. Le bord est un peu rêche. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1654,18 +1650,18 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1688,30 +1684,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>avant</t>
+          <t>seau</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1720,10 +1716,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1732,33 +1728,50 @@
         <v>50</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_reprend_sans_foncer; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah cherche le manteau.
-narrateur|Elle le prend.
+          <t>narrateur|Sarah refuse de pousser plus fort.
+narrateur|Elle pose un genou au sol.
+narrateur|Le seau vert est froid, vide.
+enfant-f|Je le tiens.
+maman|Le manteau, près du crochet ?
+narrateur|Sarah se penche.
+narrateur|Le manteau rouge est un peu mouillé.
+narrateur|Elle le prend, sans tirer.
 enfant-f|Le manteau.
 maman|Oui.
-maman|Tu cherches le doudou.
-narrateur|Sarah cherche le doudou.
-narrateur|Elle le prend.
-enfant-f|Le doudou.
-maman|Son oreille est mouillée.
-enfant-f|Un peu.
-maman|Tu as repris tes affaires.
-enfant-f|Avant de partir.
-maman|Oui.
-narrateur|Ses affaires sont dans ses mains.
-narrateur|Elles marchent vers la maison.
-narrateur|Les bottes font poum, poum.
+narrateur|Le doudou beige attend près du pot.
+enfant-f|Toi aussi.
+narrateur|Elle le ramasse, une oreille mouillée.
+enfant-f|Son oreille est froide.
+maman|Tu le serres ?
+enfant-f|Oui, maman.
+narrateur|Sarah appuie le seau contre sa hanche.
+narrateur|Le plastique fait un petit clic.
+maman|On met tes bottes ?
+narrateur|Sarah enfile ses bottes rouges.
+narrateur|Une semelle est froide.
+maman|Tu as fini tes bottes ?
+enfant-f|Oui, maman.
 maman|Tu tiens tout ?
-enfant-f|Oui.</t>
+enfant-f|Oui.
+maman|Merci, Sarah.
+maman|Le seau est prêt ?
+enfant-f|Oui, maman.
+narrateur|Sarah pose la main sur le bord.
+narrateur|Le bord est un peu rêche.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>manteau,doudou,bottes</t>
         </is>
       </c>
     </row>
@@ -1785,17 +1798,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah tient le seau. Le doudou est contre elle. Maman ouvre la porte. La gouttière fait encore plic. Tu poses le seau ? Sarah pose le seau. Elle pose le manteau. Merci, Sarah. On donne de l'eau au doudou ? Oui, maman. Maman prend une soucoupe. Sarah verse une goutte. Ploc. Il boit. Bravo. Tu as repris tes affaires. Les bottes s'arrêtent. La maison est calme. Tu poses les bottes ? Sarah pose les bottes. Elles sont un peu mouillées.</t>
+          <t>On ouvre la porte ? Oui. Pour l'eau du tuyau. Maman ouvre la porte. L'air sent la terre mouillée. Le jardin luisant s'ouvre. Un tuyau de zinc pend au mur. Sarah marche près de maman. L'herbe est un peu froide. Je le vois ! Le tuyau laisse une goutte, lente. Elle tend le seau, trop vite. Le seau penche. L'eau tombe à côté, dans l'herbe. Elle part ! Sarah veut foncer, sous le tuyau. Sarah refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. L'envie et l'inquiétude se bousculent. Personne ne dit la suite. Elle lève les yeux vers le zinc. Un point de gouttière brille, dehors. Comme au rebord ! Tu le vois, toi ? Oui, sur ce tuyau. Sarah s'accroupit, lente. Elle écoute le jardin, un instant. Une goutte tic, plus loin. Elle tient le seau, sans bouger. La goutte tombe au fond. Ça fait ploc. Ploc, maman. Tu le tiens sans presser ? Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sarah tient le seau. Le doudou est contre elle. Maman ouvre la porte. La gouttière fait encore plic. Tu poses le seau ? Sarah pose le seau. Elle pose le manteau. Merci, Sarah. On donne de l'eau au doudou ? Oui, maman. Maman prend une soucoupe. Sarah verse une goutte. Ploc. Il boit. Bravo. Tu as repris tes affaires. Les bottes s'arrêtent. La maison est calme. Tu poses les bottes ? Sarah pose les bottes. Elles sont un peu mouillées.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;On ouvre la porte ? Oui. Pour l'eau du tuyau. Maman ouvre la porte. L'air sent la terre mouillée. Le jardin luisant s'ouvre. Un tuyau de zinc pend au mur. Sarah marche près de maman. L'herbe est un peu froide. Je le vois ! Le tuyau laisse une goutte, lente. Elle tend le seau, trop vite. Le seau penche. L'eau tombe à côté, dans l'herbe. Elle part ! Sarah veut foncer, sous le tuyau. Sarah refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. L'envie et l'inquiétude se bousculent. Personne ne dit la suite. Elle lève les yeux vers le zinc. Un &lt;emphasis level="moderate"&gt;point de gouttière&lt;/emphasis&gt; brille, dehors. Comme au rebord ! Tu le vois, toi ? Oui, sur ce tuyau. Sarah s'accroupit, lente. Elle écoute le jardin, un instant. Une goutte tic, plus loin. Elle tient le seau, sans bouger. La goutte tombe au fond. Ça fait ploc. Ploc, maman. Tu le tiens sans presser ? Oui, maman.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Léonie tient le seau. Le doudou est contre elle. Maman est à côté.&lt;/slow&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;On ouvre la porte ? Oui. Pour l'eau du tuyau. Maman ouvre la porte. L'air sent la terre mouillée. Le jardin luisant s'ouvre. Un tuyau de zinc pend au mur. Sarah marche près de maman. L'herbe est un peu froide. Je le vois ! Le tuyau laisse une goutte, lente. Elle tend le seau, trop vite. Le seau penche. L'eau tombe à côté, dans l'herbe. Elle part ! Sarah veut foncer, sous le tuyau. Sarah refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. L'envie et l'inquiétude se bousculent. Personne ne dit la suite. Elle lève les yeux vers le zinc. Un &lt;emphasis&gt;point de gouttière&lt;/emphasis&gt; brille, dehors. Comme au rebord ! Tu le vois, toi ? Oui, sur ce tuyau. Sarah s'accroupit, lente. Elle écoute le jardin, un instant. Une goutte tic, plus loin. Elle tient le seau, sans bouger. La goutte tombe au fond. Ça fait ploc. Ploc, maman. Tu le tiens sans presser ? Oui, maman.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1842,30 +1855,34 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1874,28 +1891,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>point de gouttière</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1904,44 +1925,67 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_retrouve_le_point; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sarah tient le seau.
-narrateur|Le doudou est contre elle.
+          <t>maman|On ouvre la porte ?
+enfant-f|Oui.
+enfant-f|Pour l'eau du tuyau.
 narrateur|Maman ouvre la porte.
-narrateur|La gouttière fait encore plic.
-maman|Tu poses le seau ?
-narrateur|Sarah pose le seau.
-narrateur|Elle pose le manteau.
-maman|Merci, Sarah.
-maman|On donne de l'eau au doudou ?
-enfant-f|Oui, maman.
-narrateur|Maman prend une soucoupe.
-narrateur|Sarah verse une goutte.
-narrateur|Ploc.
-enfant-f|Il boit.
-maman|Bravo.
-maman|Tu as repris tes affaires.
-narrateur|Les bottes s'arrêtent.
-narrateur|La maison est calme.
-maman|Tu poses les bottes ?
-narrateur|Sarah pose les bottes.
-narrateur|Elles sont un peu mouillées.</t>
+narrateur|L'air sent la terre mouillée.
+narrateur|Le jardin luisant s'ouvre.
+narrateur|Un tuyau de zinc pend au mur.
+narrateur|Sarah marche près de maman.
+narrateur|L'herbe est un peu froide.
+enfant-f|Je le vois !
+narrateur|Le tuyau laisse une goutte, lente.
+narrateur|Elle tend le seau, trop vite.
+narrateur|Le seau penche.
+narrateur|L'eau tombe à côté, dans l'herbe.
+enfant-f|Elle part !
+narrateur|Sarah veut foncer, sous le tuyau.
+narrateur|Sarah refuse de foncer.
+narrateur|Ses épaules se serrent un peu.
+narrateur|Ça tape, dans sa poitrine.
+narrateur|L'envie et l'inquiétude se bousculent.
+narrateur|Personne ne dit la suite.
+narrateur|Elle lève les yeux vers le zinc.
+narrateur|Un point de gouttière brille, dehors.
+enfant-f|Comme au rebord !
+maman|Tu le vois, toi ?
+enfant-f|Oui, sur ce tuyau.
+narrateur|Sarah s'accroupit, lente.
+narrateur|Elle écoute le jardin, un instant.
+narrateur|Une goutte tic, plus loin.
+narrateur|Elle tient le seau, sans bouger.
+narrateur|La goutte tombe au fond.
+narrateur|Ça fait ploc.
+enfant-f|Ploc, maman.
+maman|Tu le tiens sans presser ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>porte,jardin,gouttiere</t>
         </is>
       </c>
     </row>
@@ -1968,17 +2012,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a de l'eau. Et toi, tu as repris tes affaires. La gouttière fait encore plic.</t>
+          <t>Sarah tient le seau, un peu plein. L'eau tremble, claire. Elle brille, maman. Tu la portes à la maison ? Oui. Elles rentrent dans la maison. La maison est tiède. Sarah pose le seau près de la cuvette. On donne de l'eau au doudou ? Oui, maman. Maman prend une soucoupe. Sarah verse une goutte. Ploc. Il boit. Le doudou beige a le museau frais. Comme sur le zinc, maman. Sur l'eau, un point de gouttière dore. Tu le vois, sur l'eau ? Oui. C'est mon seau vert. La soucoupe garde la goutte. Le point de gouttière dore, mince.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a de l'eau. Et toi, tu as repris tes affaires. La gouttière fait encore plic.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Sarah tient le seau, un peu plein. L'eau tremble, claire. Elle brille, maman. Tu la portes à la maison ? Oui. Elles rentrent dans la maison. La maison est tiède. Sarah pose le seau près de la cuvette. On donne de l'eau au doudou ? Oui, maman. Maman prend une soucoupe. Sarah verse une goutte. Ploc. Il boit. Le doudou beige a le museau frais. Comme sur le zinc, maman. Sur l'eau, un &lt;emphasis level="moderate"&gt;point de gouttière&lt;/emphasis&gt; dore. Tu le vois, sur l'eau ? Oui. C'est mon seau vert. La soucoupe garde la goutte. Le point de gouttière dore, mince.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Sarah tient le seau, un peu plein. L'eau tremble, claire. Elle brille, maman. Tu la portes à la maison ? Oui. Elles rentrent dans la maison. La maison est tiède. Sarah pose le seau près de la cuvette. On donne de l'eau au doudou ? Oui, maman. Maman prend une soucoupe. Sarah verse une goutte. Ploc. Il boit. Le doudou beige a le museau frais. Comme sur le zinc, maman. Sur l'eau, un &lt;emphasis&gt;point de gouttière&lt;/emphasis&gt; dore. Tu le vois, sur l'eau ? Oui. C'est mon seau vert. La soucoupe garde la goutte. Le point de gouttière dore, mince.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2025,7 +2069,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2033,10 +2077,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2045,12 +2089,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2059,17 +2103,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>point de gouttière</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2078,11 +2126,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2091,26 +2139,54 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=le_point_de_gouttiere_est_sur_l_eau; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|Le doudou a de l'eau.
-maman|Et toi, tu as repris tes affaires.
-narrateur|La gouttière fait encore plic.</t>
+          <t>narrateur|Sarah tient le seau, un peu plein.
+narrateur|L'eau tremble, claire.
+enfant-f|Elle brille, maman.
+maman|Tu la portes à la maison ?
+enfant-f|Oui.
+narrateur|Elles rentrent dans la maison.
+narrateur|La maison est tiède.
+narrateur|Sarah pose le seau près de la cuvette.
+maman|On donne de l'eau au doudou ?
+enfant-f|Oui, maman.
+narrateur|Maman prend une soucoupe.
+narrateur|Sarah verse une goutte.
+narrateur|Ploc.
+enfant-f|Il boit.
+narrateur|Le doudou beige a le museau frais.
+enfant-f|Comme sur le zinc, maman.
+narrateur|Sur l'eau, un point de gouttière dore.
+maman|Tu le vois, sur l'eau ?
+enfant-f|Oui.
+enfant-f|C'est mon seau vert.
+narrateur|La soucoupe garde la goutte.
+narrateur|Le point de gouttière dore, mince.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>soucoupe,eau,doudou</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2223,6 +2299,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.003-06.xlsx
@@ -2207,7 +2207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2306,6 +2306,13 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
